--- a/artfynd/A 26736-2024 artfynd.xlsx
+++ b/artfynd/A 26736-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675888</v>
+        <v>118675884</v>
       </c>
       <c r="B2" t="n">
-        <v>91771</v>
+        <v>91405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748450</v>
+        <v>748538</v>
       </c>
       <c r="R2" t="n">
-        <v>7294708</v>
+        <v>7294741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675884</v>
+        <v>118675885</v>
       </c>
       <c r="B3" t="n">
-        <v>91405</v>
+        <v>91783</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748538</v>
+        <v>748524</v>
       </c>
       <c r="R3" t="n">
-        <v>7294741</v>
+        <v>7294733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675886</v>
+        <v>118675883</v>
       </c>
       <c r="B4" t="n">
-        <v>91822</v>
+        <v>91773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748477</v>
+        <v>748542</v>
       </c>
       <c r="R4" t="n">
-        <v>7294730</v>
+        <v>7294747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118675885</v>
+        <v>118675888</v>
       </c>
       <c r="B5" t="n">
-        <v>91783</v>
+        <v>91771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748524</v>
+        <v>748450</v>
       </c>
       <c r="R5" t="n">
-        <v>7294733</v>
+        <v>7294708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118675887</v>
+        <v>118675886</v>
       </c>
       <c r="B6" t="n">
-        <v>91823</v>
+        <v>91822</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118675883</v>
+        <v>118675887</v>
       </c>
       <c r="B7" t="n">
-        <v>91773</v>
+        <v>91823</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748542</v>
+        <v>748477</v>
       </c>
       <c r="R7" t="n">
-        <v>7294747</v>
+        <v>7294730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 26736-2024 artfynd.xlsx
+++ b/artfynd/A 26736-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675884</v>
+        <v>118675886</v>
       </c>
       <c r="B2" t="n">
-        <v>91405</v>
+        <v>91822</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748538</v>
+        <v>748477</v>
       </c>
       <c r="R2" t="n">
-        <v>7294741</v>
+        <v>7294730</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675885</v>
+        <v>118675884</v>
       </c>
       <c r="B3" t="n">
-        <v>91783</v>
+        <v>91405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748524</v>
+        <v>748538</v>
       </c>
       <c r="R3" t="n">
-        <v>7294733</v>
+        <v>7294741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675883</v>
+        <v>118675885</v>
       </c>
       <c r="B4" t="n">
-        <v>91773</v>
+        <v>91783</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748542</v>
+        <v>748524</v>
       </c>
       <c r="R4" t="n">
-        <v>7294747</v>
+        <v>7294733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118675886</v>
+        <v>118675887</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>91823</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118675887</v>
+        <v>118675883</v>
       </c>
       <c r="B7" t="n">
-        <v>91823</v>
+        <v>91773</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748477</v>
+        <v>748542</v>
       </c>
       <c r="R7" t="n">
-        <v>7294730</v>
+        <v>7294747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 26736-2024 artfynd.xlsx
+++ b/artfynd/A 26736-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675886</v>
+        <v>118675888</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748477</v>
+        <v>748450</v>
       </c>
       <c r="R2" t="n">
-        <v>7294730</v>
+        <v>7294708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>118675884</v>
       </c>
       <c r="B3" t="n">
-        <v>91405</v>
+        <v>91412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>118675885</v>
       </c>
       <c r="B4" t="n">
-        <v>91783</v>
+        <v>91790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118675888</v>
+        <v>118675883</v>
       </c>
       <c r="B5" t="n">
-        <v>91771</v>
+        <v>91780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748450</v>
+        <v>748542</v>
       </c>
       <c r="R5" t="n">
-        <v>7294708</v>
+        <v>7294747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>118675887</v>
       </c>
       <c r="B6" t="n">
-        <v>91823</v>
+        <v>91830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118675883</v>
+        <v>118675886</v>
       </c>
       <c r="B7" t="n">
-        <v>91773</v>
+        <v>91829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748542</v>
+        <v>748477</v>
       </c>
       <c r="R7" t="n">
-        <v>7294747</v>
+        <v>7294730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 26736-2024 artfynd.xlsx
+++ b/artfynd/A 26736-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675888</v>
+        <v>118675887</v>
       </c>
       <c r="B2" t="n">
-        <v>91778</v>
+        <v>91830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>748450</v>
+        <v>748477</v>
       </c>
       <c r="R2" t="n">
-        <v>7294708</v>
+        <v>7294730</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675884</v>
+        <v>118675885</v>
       </c>
       <c r="B3" t="n">
-        <v>91412</v>
+        <v>91790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>748538</v>
+        <v>748524</v>
       </c>
       <c r="R3" t="n">
-        <v>7294741</v>
+        <v>7294733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675885</v>
+        <v>118675886</v>
       </c>
       <c r="B4" t="n">
-        <v>91790</v>
+        <v>91829</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>748524</v>
+        <v>748477</v>
       </c>
       <c r="R4" t="n">
-        <v>7294733</v>
+        <v>7294730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118675883</v>
+        <v>118675888</v>
       </c>
       <c r="B5" t="n">
-        <v>91780</v>
+        <v>91778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>748542</v>
+        <v>748450</v>
       </c>
       <c r="R5" t="n">
-        <v>7294747</v>
+        <v>7294708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118675887</v>
+        <v>118675884</v>
       </c>
       <c r="B6" t="n">
-        <v>91830</v>
+        <v>91412</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>748477</v>
+        <v>748538</v>
       </c>
       <c r="R6" t="n">
-        <v>7294730</v>
+        <v>7294741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118675886</v>
+        <v>118675883</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>91780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>748477</v>
+        <v>748542</v>
       </c>
       <c r="R7" t="n">
-        <v>7294730</v>
+        <v>7294747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
